--- a/data/dividends_info_20260421.xlsx
+++ b/data/dividends_info_20260421.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>37.79999923706055</v>
+        <v>37.61000061035156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2380952429008533</v>
+        <v>0.2392980551434208</v>
       </c>
       <c r="J2" t="n">
         <v>328</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.220000267028809</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6507592002417079</v>
+        <v>0.6437768451142812</v>
       </c>
       <c r="J4" t="n">
         <v>237</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37.80500030517578</v>
+        <v>37.61000061035156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2380637462597199</v>
+        <v>0.2392980551434208</v>
       </c>
       <c r="J6" t="n">
         <v>237</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.115000009536743</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I7" t="n">
-        <v>3.640661922118176</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J7" t="n">
         <v>216</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6.019999980926514</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I8" t="n">
-        <v>3.322259146738715</v>
+        <v>3.36134464556733</v>
       </c>
       <c r="J8" t="n">
         <v>209</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.699999809265137</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I9" t="n">
-        <v>1.052631614170798</v>
+        <v>1.034482724601393</v>
       </c>
       <c r="J9" t="n">
         <v>181</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>37.80500030517578</v>
+        <v>37.61000061035156</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2380637462597199</v>
+        <v>0.2392980551434208</v>
       </c>
       <c r="J11" t="n">
         <v>153</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.150000095367432</v>
+        <v>6.110000133514404</v>
       </c>
       <c r="I13" t="n">
-        <v>4.065040587370328</v>
+        <v>4.091652938413322</v>
       </c>
       <c r="J13" t="n">
         <v>97</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.77400016784668</v>
+        <v>9.694000244140625</v>
       </c>
       <c r="I14" t="n">
-        <v>2.660118636536517</v>
+        <v>2.68207131681426</v>
       </c>
       <c r="J14" t="n">
         <v>90</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>16.20000076293945</v>
+        <v>16.28000068664551</v>
       </c>
       <c r="I15" t="n">
-        <v>3.703703529277682</v>
+        <v>3.68550353005931</v>
       </c>
       <c r="J15" t="n">
         <v>90</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4.004000186920166</v>
+        <v>3.970000028610229</v>
       </c>
       <c r="I16" t="n">
-        <v>5.494505238003539</v>
+        <v>5.541561672910491</v>
       </c>
       <c r="J16" t="n">
         <v>90</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6.119999885559082</v>
+        <v>6.025000095367432</v>
       </c>
       <c r="I18" t="n">
-        <v>1.633986958659309</v>
+        <v>1.659751011072832</v>
       </c>
       <c r="J18" t="n">
         <v>90</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>18.64999961853027</v>
+        <v>18.25</v>
       </c>
       <c r="I19" t="n">
-        <v>2.016085832122022</v>
+        <v>2.06027397260274</v>
       </c>
       <c r="J19" t="n">
         <v>90</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.630000114440918</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="I20" t="n">
-        <v>2.131438677811048</v>
+        <v>2.127659624835675</v>
       </c>
       <c r="J20" t="n">
         <v>83</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.399999618530273</v>
+        <v>9.5</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5319149152031317</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="J21" t="n">
         <v>83</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.480000019073486</v>
+        <v>4.599999904632568</v>
       </c>
       <c r="I23" t="n">
-        <v>1.562499993347696</v>
+        <v>1.521739161983556</v>
       </c>
       <c r="J23" t="n">
         <v>76</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>35.15000152587891</v>
+        <v>35.5</v>
       </c>
       <c r="I24" t="n">
-        <v>0.426742513480586</v>
+        <v>0.4225352112676056</v>
       </c>
       <c r="J24" t="n">
         <v>76</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.050000190734863</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6611570039494726</v>
+        <v>0.6557377151698397</v>
       </c>
       <c r="J25" t="n">
         <v>69</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22.78000068664551</v>
+        <v>22.42000007629395</v>
       </c>
       <c r="I26" t="n">
-        <v>1.097453873855936</v>
+        <v>1.115075821361573</v>
       </c>
       <c r="J26" t="n">
         <v>62</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>26.54999923706055</v>
+        <v>26.29999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7344632979416583</v>
+        <v>0.7414448884288045</v>
       </c>
       <c r="J27" t="n">
         <v>62</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.929999947547913</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="I28" t="n">
-        <v>1.709844606054362</v>
+        <v>1.692307650925376</v>
       </c>
       <c r="J28" t="n">
         <v>62</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5.105000019073486</v>
+        <v>5.110000133514404</v>
       </c>
       <c r="I29" t="n">
-        <v>5.680705169764769</v>
+        <v>5.67514662275659</v>
       </c>
       <c r="J29" t="n">
         <v>62</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.142000198364258</v>
+        <v>4.111999988555908</v>
       </c>
       <c r="I30" t="n">
-        <v>3.862867994627005</v>
+        <v>3.891050594486756</v>
       </c>
       <c r="J30" t="n">
         <v>62</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.582000017166138</v>
+        <v>2.572000026702881</v>
       </c>
       <c r="I31" t="n">
-        <v>5.367931800098119</v>
+        <v>5.388802432388589</v>
       </c>
       <c r="J31" t="n">
         <v>62</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>56.77000045776367</v>
+        <v>55.27000045776367</v>
       </c>
       <c r="I32" t="n">
-        <v>1.109741051470863</v>
+        <v>1.139858865174851</v>
       </c>
       <c r="J32" t="n">
         <v>62</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.377500057220459</v>
+        <v>5.380000114440918</v>
       </c>
       <c r="I33" t="n">
-        <v>2.603440232641554</v>
+        <v>2.602230427917911</v>
       </c>
       <c r="J33" t="n">
         <v>62</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>18.10000038146973</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="I34" t="n">
-        <v>4.30939217437002</v>
+        <v>4.13793095074295</v>
       </c>
       <c r="J34" t="n">
         <v>62</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>22.38999938964844</v>
+        <v>22.23999977111816</v>
       </c>
       <c r="I35" t="n">
-        <v>3.796337754225131</v>
+        <v>3.821942485376494</v>
       </c>
       <c r="J35" t="n">
         <v>62</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>37.80500030517578</v>
+        <v>37.61000061035156</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2380637462597199</v>
+        <v>0.2392980551434208</v>
       </c>
       <c r="J36" t="n">
         <v>62</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6.64799976348877</v>
+        <v>6.604000091552734</v>
       </c>
       <c r="I37" t="n">
-        <v>2.727136077767495</v>
+        <v>2.745305837168344</v>
       </c>
       <c r="J37" t="n">
         <v>62</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8.479999542236328</v>
+        <v>8.409999847412109</v>
       </c>
       <c r="I38" t="n">
-        <v>3.066037901358581</v>
+        <v>3.091557725533207</v>
       </c>
       <c r="J38" t="n">
         <v>62</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>10.11499977111816</v>
+        <v>10.05500030517578</v>
       </c>
       <c r="I39" t="n">
-        <v>2.738507229539749</v>
+        <v>2.754848250550675</v>
       </c>
       <c r="J39" t="n">
         <v>62</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4.130000114440918</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I41" t="n">
-        <v>2.663438182855615</v>
+        <v>2.682926891674109</v>
       </c>
       <c r="J41" t="n">
         <v>55</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.70000076293945</v>
+        <v>28.29999923706055</v>
       </c>
       <c r="I43" t="n">
-        <v>3.867595716002044</v>
+        <v>3.922261589839156</v>
       </c>
       <c r="J43" t="n">
         <v>44</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.9010000228881836</v>
+        <v>0.9120000004768372</v>
       </c>
       <c r="I44" t="n">
-        <v>3.329633655705586</v>
+        <v>3.289473682490633</v>
       </c>
       <c r="J44" t="n">
         <v>41</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.5360000133514404</v>
+        <v>0.5329999923706055</v>
       </c>
       <c r="I45" t="n">
-        <v>4.291044669232039</v>
+        <v>4.315197059891821</v>
       </c>
       <c r="J45" t="n">
         <v>41</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.840000152587891</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I47" t="n">
-        <v>2.262443399861825</v>
+        <v>2.227171605736999</v>
       </c>
       <c r="J47" t="n">
         <v>41</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>8.699999809265137</v>
+        <v>8.550000190734863</v>
       </c>
       <c r="I49" t="n">
-        <v>3.448275937667407</v>
+        <v>3.508771851550278</v>
       </c>
       <c r="J49" t="n">
         <v>34</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>13.39999961853027</v>
+        <v>13.38000011444092</v>
       </c>
       <c r="I50" t="n">
-        <v>1.865671694902781</v>
+        <v>1.868460372658571</v>
       </c>
       <c r="J50" t="n">
         <v>34</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.369999885559082</v>
+        <v>3.430000066757202</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8902077453638549</v>
+        <v>0.8746355514903141</v>
       </c>
       <c r="J51" t="n">
         <v>34</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.779999971389771</v>
+        <v>3.759999990463257</v>
       </c>
       <c r="I52" t="n">
-        <v>3.968253998289063</v>
+        <v>3.989361712246148</v>
       </c>
       <c r="J52" t="n">
         <v>34</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>13.39999961853027</v>
+        <v>13.5</v>
       </c>
       <c r="I53" t="n">
-        <v>4.328358332174453</v>
+        <v>4.296296296296296</v>
       </c>
       <c r="J53" t="n">
         <v>34</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2.404000043869019</v>
+        <v>2.385999917984009</v>
       </c>
       <c r="I54" t="n">
-        <v>4.326123049175219</v>
+        <v>4.358759579835702</v>
       </c>
       <c r="J54" t="n">
         <v>27</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>9.972000122070312</v>
+        <v>10.01500034332275</v>
       </c>
       <c r="I55" t="n">
-        <v>2.908142764240083</v>
+        <v>2.895656415961584</v>
       </c>
       <c r="J55" t="n">
         <v>27</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2.115000009536743</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I56" t="n">
-        <v>3.640661922118176</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J56" t="n">
         <v>27</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>37.66999816894531</v>
+        <v>37.86999893188477</v>
       </c>
       <c r="I57" t="n">
-        <v>4.353597238430439</v>
+        <v>4.330604822434248</v>
       </c>
       <c r="J57" t="n">
         <v>27</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>37.45000076293945</v>
+        <v>37.34000015258789</v>
       </c>
       <c r="I58" t="n">
-        <v>5.340453829787906</v>
+        <v>5.35618637339879</v>
       </c>
       <c r="J58" t="n">
         <v>27</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>4.113999843597412</v>
+        <v>4.092000007629395</v>
       </c>
       <c r="I59" t="n">
-        <v>2.430724448267281</v>
+        <v>2.443792761817043</v>
       </c>
       <c r="J59" t="n">
         <v>27</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>38.4900016784668</v>
+        <v>36.86000061035156</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3857105573550958</v>
+        <v>0.4027672206774389</v>
       </c>
       <c r="J60" t="n">
         <v>27</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>23.55999946594238</v>
+        <v>23.31999969482422</v>
       </c>
       <c r="I61" t="n">
-        <v>3.904923687837616</v>
+        <v>3.945111543908769</v>
       </c>
       <c r="J61" t="n">
         <v>27</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>8.560000419616699</v>
+        <v>8.5</v>
       </c>
       <c r="I62" t="n">
-        <v>3.504672725394953</v>
+        <v>3.529411764705882</v>
       </c>
       <c r="J62" t="n">
         <v>27</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>87.40000152587891</v>
+        <v>86.58000183105469</v>
       </c>
       <c r="I63" t="n">
-        <v>1.189931329339919</v>
+        <v>1.201201175797355</v>
       </c>
       <c r="J63" t="n">
         <v>27</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>48.95000076293945</v>
+        <v>48.38000106811523</v>
       </c>
       <c r="I64" t="n">
-        <v>1.430030621225193</v>
+        <v>1.446878843624776</v>
       </c>
       <c r="J64" t="n">
         <v>27</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>56.25</v>
+        <v>56.29999923706055</v>
       </c>
       <c r="I65" t="n">
-        <v>3.911111111111112</v>
+        <v>3.907637708371066</v>
       </c>
       <c r="J65" t="n">
         <v>27</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>9.234999656677246</v>
+        <v>9.107000350952148</v>
       </c>
       <c r="I66" t="n">
-        <v>9.312398830228306</v>
+        <v>9.443285020957378</v>
       </c>
       <c r="J66" t="n">
         <v>27</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>12.38199996948242</v>
+        <v>12.15799999237061</v>
       </c>
       <c r="I67" t="n">
-        <v>4.522694244711814</v>
+        <v>4.606020729983644</v>
       </c>
       <c r="J67" t="n">
         <v>27</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>2.119999885559082</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I68" t="n">
-        <v>1.886792554682204</v>
+        <v>1.801801778581098</v>
       </c>
       <c r="J68" t="n">
         <v>27</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>9.340000152587891</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I69" t="n">
-        <v>3.211991382215097</v>
+        <v>3.260869632821905</v>
       </c>
       <c r="J69" t="n">
         <v>27</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>2.309999942779541</v>
+        <v>2.269999980926514</v>
       </c>
       <c r="I70" t="n">
-        <v>4.67532479113603</v>
+        <v>4.757709291077578</v>
       </c>
       <c r="J70" t="n">
         <v>27</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>75.69999694824219</v>
+        <v>75</v>
       </c>
       <c r="I71" t="n">
-        <v>2.72126827350927</v>
+        <v>2.746666666666667</v>
       </c>
       <c r="J71" t="n">
         <v>27</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>15.6899995803833</v>
+        <v>15.52000045776367</v>
       </c>
       <c r="I72" t="n">
-        <v>4.780114850593755</v>
+        <v>4.832474084269904</v>
       </c>
       <c r="J72" t="n">
         <v>27</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>16.27000045776367</v>
+        <v>16.13999938964844</v>
       </c>
       <c r="I73" t="n">
-        <v>1.8438843980293</v>
+        <v>1.858736129769671</v>
       </c>
       <c r="J73" t="n">
         <v>27</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>45.29999923706055</v>
+        <v>44.5</v>
       </c>
       <c r="I74" t="n">
-        <v>1.876379722551084</v>
+        <v>1.910112359550562</v>
       </c>
       <c r="J74" t="n">
         <v>27</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>34.08000183105469</v>
+        <v>33.72000122070312</v>
       </c>
       <c r="I75" t="n">
-        <v>2.494131321394048</v>
+        <v>2.520759102102653</v>
       </c>
       <c r="J75" t="n">
         <v>27</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>63.11999893188477</v>
+        <v>63.40000152587891</v>
       </c>
       <c r="I76" t="n">
-        <v>2.059569109630183</v>
+        <v>2.050473136770131</v>
       </c>
       <c r="J76" t="n">
         <v>27</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>8.079999923706055</v>
+        <v>8.159999847412109</v>
       </c>
       <c r="I77" t="n">
-        <v>7.425742644373663</v>
+        <v>7.352941313966888</v>
       </c>
       <c r="J77" t="n">
         <v>27</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>6.400000095367432</v>
+        <v>6.300000190734863</v>
       </c>
       <c r="I78" t="n">
-        <v>7.343749890569598</v>
+        <v>7.460317234453558</v>
       </c>
       <c r="J78" t="n">
         <v>27</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>6.019999980926514</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I79" t="n">
-        <v>3.322259146738715</v>
+        <v>3.36134464556733</v>
       </c>
       <c r="J79" t="n">
         <v>27</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>21.3799991607666</v>
+        <v>21.73999977111816</v>
       </c>
       <c r="I80" t="n">
-        <v>4.677268658808235</v>
+        <v>4.599816055787229</v>
       </c>
       <c r="J80" t="n">
         <v>27</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>4.920000076293945</v>
+        <v>4.880000114440918</v>
       </c>
       <c r="I81" t="n">
-        <v>4.369918631423103</v>
+        <v>4.405737601599046</v>
       </c>
       <c r="J81" t="n">
         <v>27</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>22.34499931335449</v>
+        <v>22.40500068664551</v>
       </c>
       <c r="I82" t="n">
-        <v>1.208324046976517</v>
+        <v>1.205088113034218</v>
       </c>
       <c r="J82" t="n">
         <v>27</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>8</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I83" t="n">
-        <v>2.5</v>
+        <v>2.439024446976463</v>
       </c>
       <c r="J83" t="n">
         <v>27</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>9.534999847412109</v>
+        <v>9.510000228881836</v>
       </c>
       <c r="I84" t="n">
-        <v>2.51704251537181</v>
+        <v>2.523659245255546</v>
       </c>
       <c r="J84" t="n">
         <v>27</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>21.96999931335449</v>
+        <v>21.79000091552734</v>
       </c>
       <c r="I85" t="n">
-        <v>3.595812583934846</v>
+        <v>3.625516139547538</v>
       </c>
       <c r="J85" t="n">
         <v>27</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>4.829999923706055</v>
+        <v>4.820000171661377</v>
       </c>
       <c r="I86" t="n">
-        <v>1.925465868923683</v>
+        <v>1.929460512196297</v>
       </c>
       <c r="J86" t="n">
         <v>27</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.699999809265137</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I87" t="n">
-        <v>1.052631614170798</v>
+        <v>1.034482724601393</v>
       </c>
       <c r="J87" t="n">
         <v>27</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>37.41999816894531</v>
+        <v>36.90000152587891</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9353287469972764</v>
+        <v>0.9485094458723426</v>
       </c>
       <c r="J88" t="n">
         <v>27</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>7.340000152587891</v>
+        <v>7.269999980926514</v>
       </c>
       <c r="I89" t="n">
-        <v>7.551770960175913</v>
+        <v>7.624484201571595</v>
       </c>
       <c r="J89" t="n">
         <v>27</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>2.210000038146973</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I90" t="n">
-        <v>2.71493207983419</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J90" t="n">
         <v>27</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>12.85000038146973</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="I91" t="n">
-        <v>1.556420187258585</v>
+        <v>1.562499976716936</v>
       </c>
       <c r="J91" t="n">
         <v>27</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>6.324999809265137</v>
+        <v>6.255000114440918</v>
       </c>
       <c r="I92" t="n">
-        <v>1.628458547131038</v>
+        <v>1.646682623749341</v>
       </c>
       <c r="J92" t="n">
         <v>27</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>5.824999809265137</v>
+        <v>5.778999805450439</v>
       </c>
       <c r="I93" t="n">
-        <v>3.261802681912358</v>
+        <v>3.287766160171909</v>
       </c>
       <c r="J93" t="n">
         <v>27</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>10.47000026702881</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I94" t="n">
-        <v>4.126074393335174</v>
+        <v>4.194174679614045</v>
       </c>
       <c r="J94" t="n">
         <v>27</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>26.02000045776367</v>
+        <v>25.53000068664551</v>
       </c>
       <c r="I95" t="n">
-        <v>1.691006888006091</v>
+        <v>1.723462546674194</v>
       </c>
       <c r="J95" t="n">
         <v>27</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>8.619999885559082</v>
+        <v>8.449999809265137</v>
       </c>
       <c r="I97" t="n">
-        <v>5.452436267283272</v>
+        <v>5.562130303064161</v>
       </c>
       <c r="J97" t="n">
         <v>27</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>57.52000045776367</v>
+        <v>57.58000183105469</v>
       </c>
       <c r="I98" t="n">
-        <v>2.433936002883041</v>
+        <v>2.431399714275341</v>
       </c>
       <c r="J98" t="n">
         <v>27</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>3.805999994277954</v>
+        <v>3.796999931335449</v>
       </c>
       <c r="I99" t="n">
-        <v>7.882291131135793</v>
+        <v>7.900974596396332</v>
       </c>
       <c r="J99" t="n">
         <v>27</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>13.35000038146973</v>
+        <v>12.69999980926514</v>
       </c>
       <c r="I100" t="n">
-        <v>0.8988763788094286</v>
+        <v>0.9448819039544819</v>
       </c>
       <c r="J100" t="n">
         <v>27</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>2.680000066757202</v>
+        <v>2.619999885559082</v>
       </c>
       <c r="I103" t="n">
-        <v>1.305970116722794</v>
+        <v>1.33587792094622</v>
       </c>
       <c r="J103" t="n">
         <v>27</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>6.130000114440918</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="I104" t="n">
-        <v>5.383360421520929</v>
+        <v>5.374592950746838</v>
       </c>
       <c r="J104" t="n">
         <v>27</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.9909999966621399</v>
+        <v>0.9959999918937683</v>
       </c>
       <c r="I105" t="n">
-        <v>7.063572173135436</v>
+        <v>7.028112506999507</v>
       </c>
       <c r="J105" t="n">
         <v>27</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>50.15000152587891</v>
+        <v>49.41999816894531</v>
       </c>
       <c r="I106" t="n">
-        <v>1.415752698698561</v>
+        <v>1.43666537091487</v>
       </c>
       <c r="J106" t="n">
         <v>27</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>94.69999694824219</v>
+        <v>95.90000152587891</v>
       </c>
       <c r="I107" t="n">
-        <v>1.425554428199017</v>
+        <v>1.40771634882164</v>
       </c>
       <c r="J107" t="n">
         <v>27</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>7.179999828338623</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I108" t="n">
-        <v>1.114206154772446</v>
+        <v>1.111111140545505</v>
       </c>
       <c r="J108" t="n">
         <v>27</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.953000068664551</v>
+        <v>3.920000076293945</v>
       </c>
       <c r="I110" t="n">
-        <v>4.300531167393363</v>
+        <v>4.336734609472808</v>
       </c>
       <c r="J110" t="n">
         <v>27</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>58</v>
+        <v>58.20000076293945</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7758620689655172</v>
+        <v>0.7731958661528929</v>
       </c>
       <c r="J112" t="n">
         <v>27</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>34.52000045776367</v>
+        <v>34.40000152587891</v>
       </c>
       <c r="I114" t="n">
-        <v>3.041714907520667</v>
+        <v>3.052325446003517</v>
       </c>
       <c r="J114" t="n">
         <v>27</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>19.70000076293945</v>
+        <v>19.77000045776367</v>
       </c>
       <c r="I116" t="n">
-        <v>1.928933935448741</v>
+        <v>1.922104153774939</v>
       </c>
       <c r="J116" t="n">
         <v>27</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>25.42000007629395</v>
+        <v>25.81999969482422</v>
       </c>
       <c r="I117" t="n">
-        <v>2.360346177022812</v>
+        <v>2.323780042957451</v>
       </c>
       <c r="J117" t="n">
         <v>27</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>35.45000076293945</v>
+        <v>36.09999847412109</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9873060436317422</v>
+        <v>0.9695291268527435</v>
       </c>
       <c r="J118" t="n">
         <v>27</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>3.519999980926514</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="I119" t="n">
-        <v>0.482954548071485</v>
+        <v>0.488505744448992</v>
       </c>
       <c r="J119" t="n">
         <v>27</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>2.910000085830688</v>
+        <v>2.950000047683716</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3436426015480821</v>
+        <v>0.3389830453681453</v>
       </c>
       <c r="J120" t="n">
         <v>27</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>22.61000061035156</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="I121" t="n">
-        <v>4.95356023779685</v>
+        <v>4.955752128740292</v>
       </c>
       <c r="J121" t="n">
         <v>27</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>1.519999980926514</v>
+        <v>1.509999990463257</v>
       </c>
       <c r="I122" t="n">
-        <v>6.578947450975964</v>
+        <v>6.622516598117379</v>
       </c>
       <c r="J122" t="n">
         <v>27</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>2.619999885559082</v>
+        <v>2.595999956130981</v>
       </c>
       <c r="I123" t="n">
-        <v>9.923664555600489</v>
+        <v>10.01540848974042</v>
       </c>
       <c r="J123" t="n">
         <v>27</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2.5</v>
+        <v>2.477999925613403</v>
       </c>
       <c r="I124" t="n">
-        <v>3.691999999999999</v>
+        <v>3.724778158625331</v>
       </c>
       <c r="J124" t="n">
         <v>27</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>9.399999618530273</v>
+        <v>9.359999656677246</v>
       </c>
       <c r="I125" t="n">
-        <v>3.723404406421921</v>
+        <v>3.739316376473546</v>
       </c>
       <c r="J125" t="n">
         <v>20</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>6.099999904632568</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I127" t="n">
-        <v>4.918032863773797</v>
+        <v>4.958677529621045</v>
       </c>
       <c r="J127" t="n">
         <v>20</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>11.69999980926514</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="I128" t="n">
-        <v>1.70940173726859</v>
+        <v>1.724137874335655</v>
       </c>
       <c r="J128" t="n">
         <v>20</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9.220000267028809</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6507592002417079</v>
+        <v>0.6437768451142812</v>
       </c>
       <c r="J129" t="n">
         <v>20</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>16.45999908447266</v>
+        <v>16.47999954223633</v>
       </c>
       <c r="I131" t="n">
-        <v>3.037667240648081</v>
+        <v>3.033980666798916</v>
       </c>
       <c r="J131" t="n">
         <v>20</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>4.039999961853027</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="I132" t="n">
-        <v>2.475247548124555</v>
+        <v>2.512562802029314</v>
       </c>
       <c r="J132" t="n">
         <v>20</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>2.880000114440918</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="I133" t="n">
-        <v>3.819444292673364</v>
+        <v>3.767123189243599</v>
       </c>
       <c r="J133" t="n">
         <v>20</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>4.570000171661377</v>
+        <v>4.539999961853027</v>
       </c>
       <c r="I135" t="n">
-        <v>2.078774538983523</v>
+        <v>2.092511030798009</v>
       </c>
       <c r="J135" t="n">
         <v>20</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>1.399999976158142</v>
+        <v>1.309999942779541</v>
       </c>
       <c r="I136" t="n">
-        <v>2.142857179349783</v>
+        <v>2.290076435907805</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>7.699999809265137</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="I137" t="n">
-        <v>1.168831197784008</v>
+        <v>1.14649682921509</v>
       </c>
       <c r="J137" t="n">
         <v>20</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>8.100000381469727</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I138" t="n">
-        <v>1.234567843092561</v>
+        <v>1.190476244539363</v>
       </c>
       <c r="J138" t="n">
         <v>20</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>7.210000038146973</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="I139" t="n">
-        <v>3.05131759828037</v>
+        <v>3.081232550614696</v>
       </c>
       <c r="J139" t="n">
         <v>20</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>3.440000057220459</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="I140" t="n">
-        <v>4.651162713330911</v>
+        <v>4.705882220944735</v>
       </c>
       <c r="J140" t="n">
         <v>13</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>22.35000038146973</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="I141" t="n">
-        <v>2.729306441111956</v>
+        <v>2.753950386029287</v>
       </c>
       <c r="J141" t="n">
         <v>13</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>3.059999942779541</v>
+        <v>3.130000114440918</v>
       </c>
       <c r="I142" t="n">
-        <v>4.901960875977926</v>
+        <v>4.792332093150517</v>
       </c>
       <c r="J142" t="n">
         <v>13</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>12.80000019073486</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="I143" t="n">
-        <v>5.468749918509276</v>
+        <v>5.447470655405047</v>
       </c>
       <c r="J143" t="n">
         <v>13</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.460000038146973</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="I144" t="n">
-        <v>5.396405897900999</v>
+        <v>5.477467990514009</v>
       </c>
       <c r="J144" t="n">
         <v>13</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>7.889999866485596</v>
+        <v>7.775000095367432</v>
       </c>
       <c r="I145" t="n">
-        <v>3.422053289847073</v>
+        <v>3.472668767693955</v>
       </c>
       <c r="J145" t="n">
         <v>13</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>5.894999980926514</v>
+        <v>5.965000152587891</v>
       </c>
       <c r="I146" t="n">
-        <v>5.937234964078671</v>
+        <v>5.86756062106979</v>
       </c>
       <c r="J146" t="n">
         <v>13</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>36.59999847412109</v>
+        <v>37.40000152587891</v>
       </c>
       <c r="I147" t="n">
-        <v>3.005464606174182</v>
+        <v>2.941176350591472</v>
       </c>
       <c r="J147" t="n">
         <v>13</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>18.70000076293945</v>
+        <v>18.75</v>
       </c>
       <c r="I148" t="n">
-        <v>4.010695023533825</v>
+        <v>4</v>
       </c>
       <c r="J148" t="n">
         <v>13</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="I149" t="n">
-        <v>4</v>
+        <v>3.909090909090909</v>
       </c>
       <c r="J149" t="n">
         <v>13</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>4.400000095367432</v>
+        <v>4.445000171661377</v>
       </c>
       <c r="I150" t="n">
-        <v>3.409090835200855</v>
+        <v>3.374578047405014</v>
       </c>
       <c r="J150" t="n">
         <v>13</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>12.23999977111816</v>
+        <v>12.22000026702881</v>
       </c>
       <c r="I151" t="n">
-        <v>1.610857873259486</v>
+        <v>1.613494236428032</v>
       </c>
       <c r="J151" t="n">
         <v>13</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>29.75</v>
+        <v>29.54999923706055</v>
       </c>
       <c r="I152" t="n">
-        <v>3.697478991596639</v>
+        <v>3.722504326228272</v>
       </c>
       <c r="J152" t="n">
         <v>13</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>81.40000152587891</v>
+        <v>81</v>
       </c>
       <c r="I154" t="n">
-        <v>1.474201446566918</v>
+        <v>1.481481481481481</v>
       </c>
       <c r="J154" t="n">
         <v>13</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>10.39999961853027</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="I156" t="n">
-        <v>3.653846287868437</v>
+        <v>3.601895669478002</v>
       </c>
       <c r="J156" t="n">
         <v>13</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>30.95000076293945</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9693053072852582</v>
+        <v>0.9787928343680207</v>
       </c>
       <c r="J157" t="n">
         <v>13</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>0.2004999965429306</v>
+        <v>0.1993999928236008</v>
       </c>
       <c r="I158" t="n">
-        <v>3.49127188064623</v>
+        <v>3.51053172112827</v>
       </c>
       <c r="J158" t="n">
         <v>6</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>7.659999847412109</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I159" t="n">
-        <v>2.088772887561547</v>
+        <v>2.105263184312308</v>
       </c>
       <c r="J159" t="n">
         <v>6</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>2.214999914169312</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I160" t="n">
-        <v>2.93453735976224</v>
+        <v>2.968036452131321</v>
       </c>
       <c r="J160" t="n">
         <v>6</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>8.369999885559082</v>
+        <v>8.25</v>
       </c>
       <c r="I161" t="n">
-        <v>2.986857866406064</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="J161" t="n">
         <v>6</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>1.490000009536743</v>
+        <v>1.480000019073486</v>
       </c>
       <c r="I162" t="n">
-        <v>4.697986547111752</v>
+        <v>4.729729668775382</v>
       </c>
       <c r="J162" t="n">
         <v>6</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>6.389999866485596</v>
+        <v>6.309999942779541</v>
       </c>
       <c r="I163" t="n">
-        <v>7.824726298077257</v>
+        <v>7.923930341269561</v>
       </c>
       <c r="J163" t="n">
         <v>-1</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>18.75</v>
+        <v>18.67499923706055</v>
       </c>
       <c r="I164" t="n">
-        <v>3.466666666666666</v>
+        <v>3.48058916495201</v>
       </c>
       <c r="J164" t="n">
         <v>-1</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>12.625</v>
+        <v>12.51000022888184</v>
       </c>
       <c r="I165" t="n">
-        <v>4.277227722772277</v>
+        <v>4.316546683614778</v>
       </c>
       <c r="J165" t="n">
         <v>-1</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.423999786376953</v>
+        <v>6.380000114440918</v>
       </c>
       <c r="I166" t="n">
-        <v>1.556662567331725</v>
+        <v>1.567398091007135</v>
       </c>
       <c r="J166" t="n">
         <v>-1</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>9.159999847412109</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I167" t="n">
-        <v>1.746724919926754</v>
+        <v>1.727861728350306</v>
       </c>
       <c r="J167" t="n">
         <v>-1</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>313.0499877929688</v>
+        <v>309.2999877929688</v>
       </c>
       <c r="I168" t="n">
-        <v>1.154767654037006</v>
+        <v>1.168768232354317</v>
       </c>
       <c r="J168" t="n">
         <v>-1</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I169" t="n">
-        <v>4.689655172413794</v>
+        <v>4.857142857142858</v>
       </c>
       <c r="J169" t="n">
         <v>-1</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>13.98999977111816</v>
+        <v>14.02999973297119</v>
       </c>
       <c r="I170" t="n">
-        <v>41.61258109537984</v>
+        <v>41.4939423435551</v>
       </c>
       <c r="J170" t="n">
         <v>-1</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>14.6899995803833</v>
+        <v>14.61999988555908</v>
       </c>
       <c r="I171" t="n">
-        <v>3.982300998709326</v>
+        <v>4.001368020377581</v>
       </c>
       <c r="J171" t="n">
         <v>-1</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>20.23999977111816</v>
+        <v>19.90500068664551</v>
       </c>
       <c r="I172" t="n">
-        <v>3.112648256542917</v>
+        <v>3.165033801896195</v>
       </c>
       <c r="J172" t="n">
         <v>-1</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>120.8000030517578</v>
+        <v>119.3000030517578</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7450330937610881</v>
+        <v>0.7544006512804017</v>
       </c>
       <c r="J173" t="n">
         <v>-1</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>68.01999664306641</v>
+        <v>67.01000213623047</v>
       </c>
       <c r="I174" t="n">
-        <v>2.529844288334597</v>
+        <v>2.567974847249872</v>
       </c>
       <c r="J174" t="n">
         <v>-1</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>25.70000076293945</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5447470655405048</v>
+        <v>0.5426356749611693</v>
       </c>
       <c r="J175" t="n">
         <v>-8</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>2.140000104904175</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I177" t="n">
-        <v>1.588784968845712</v>
+        <v>1.574074011525993</v>
       </c>
       <c r="J177" t="n">
         <v>-22</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>22.34499931335449</v>
+        <v>22.40500068664551</v>
       </c>
       <c r="I178" t="n">
-        <v>1.163571304495906</v>
+        <v>1.160455219958877</v>
       </c>
       <c r="J178" t="n">
         <v>-29</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>37.80500030517578</v>
+        <v>37.61000061035156</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2380637462597199</v>
+        <v>0.2392980551434208</v>
       </c>
       <c r="J179" t="n">
         <v>-29</v>
@@ -8865,7 +8865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C638"/>
+  <dimension ref="A1:C648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10690,7 +10690,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10707,7 +10707,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10724,7 +10724,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10741,7 +10741,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10758,7 +10758,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10775,7 +10775,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10819,14 +10819,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10860,7 +10860,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10877,7 +10877,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10894,7 +10894,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10911,7 +10911,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10962,7 +10962,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10972,14 +10972,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10989,14 +10989,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11013,7 +11013,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11030,7 +11030,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11047,7 +11047,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11057,14 +11057,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11081,7 +11081,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11098,7 +11098,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11115,7 +11115,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11132,7 +11132,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11149,7 +11149,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11159,14 +11159,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11183,7 +11183,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11200,7 +11200,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11217,7 +11217,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11227,14 +11227,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11251,7 +11251,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11268,7 +11268,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11278,14 +11278,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11295,14 +11295,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11319,7 +11319,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11336,7 +11336,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11353,7 +11353,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11370,7 +11370,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11387,7 +11387,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11404,7 +11404,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11421,7 +11421,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11438,7 +11438,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11455,7 +11455,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11472,7 +11472,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11489,7 +11489,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11506,7 +11506,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11523,7 +11523,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11540,7 +11540,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11557,7 +11557,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11574,7 +11574,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11608,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11618,14 +11618,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11642,7 +11642,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11659,7 +11659,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11669,14 +11669,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11693,7 +11693,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11710,7 +11710,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11727,7 +11727,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11744,7 +11744,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11761,7 +11761,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11778,7 +11778,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11795,7 +11795,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11812,7 +11812,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11829,7 +11829,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11846,7 +11846,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11863,7 +11863,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11880,7 +11880,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11890,14 +11890,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11914,7 +11914,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11931,7 +11931,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11948,7 +11948,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11958,14 +11958,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11982,7 +11982,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11992,14 +11992,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12009,14 +12009,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12033,7 +12033,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12050,7 +12050,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12067,7 +12067,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12077,14 +12077,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12101,7 +12101,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12111,14 +12111,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12135,7 +12135,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12152,7 +12152,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12169,7 +12169,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12186,7 +12186,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12203,7 +12203,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12220,7 +12220,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12230,14 +12230,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12271,7 +12271,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12288,7 +12288,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12305,7 +12305,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12322,7 +12322,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12339,7 +12339,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12349,14 +12349,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12373,7 +12373,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12390,7 +12390,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12407,7 +12407,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12424,7 +12424,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12441,7 +12441,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12458,7 +12458,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12468,14 +12468,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12492,7 +12492,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12509,7 +12509,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12519,14 +12519,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12543,7 +12543,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12560,7 +12560,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12570,14 +12570,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12594,7 +12594,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12604,14 +12604,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12628,7 +12628,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12645,7 +12645,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12662,7 +12662,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12679,7 +12679,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12689,14 +12689,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12713,7 +12713,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12730,7 +12730,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12740,14 +12740,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12764,7 +12764,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12781,7 +12781,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12798,7 +12798,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12815,7 +12815,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12832,7 +12832,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12842,14 +12842,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12866,7 +12866,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12883,7 +12883,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12900,7 +12900,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12917,7 +12917,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12927,14 +12927,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12951,7 +12951,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12968,7 +12968,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12985,7 +12985,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -13002,7 +13002,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13019,7 +13019,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13036,7 +13036,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13053,7 +13053,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13070,7 +13070,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13087,7 +13087,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13104,7 +13104,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13121,7 +13121,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13138,7 +13138,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13155,7 +13155,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13165,14 +13165,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13189,7 +13189,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13199,14 +13199,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13216,14 +13216,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13233,14 +13233,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13250,14 +13250,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13274,12 +13274,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -13291,12 +13291,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -13308,12 +13308,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -13325,46 +13325,46 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -13376,12 +13376,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -13393,12 +13393,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -13410,12 +13410,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -13432,19 +13432,19 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13461,7 +13461,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13478,7 +13478,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13495,7 +13495,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13512,7 +13512,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13529,7 +13529,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13546,7 +13546,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13556,14 +13556,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13580,7 +13580,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13597,7 +13597,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13614,7 +13614,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13631,7 +13631,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13648,7 +13648,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13665,7 +13665,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13682,7 +13682,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13692,14 +13692,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13716,7 +13716,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13733,7 +13733,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13750,7 +13750,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13760,14 +13760,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13784,7 +13784,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13801,7 +13801,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13818,7 +13818,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13835,7 +13835,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13852,7 +13852,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13862,14 +13862,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13886,7 +13886,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13896,14 +13896,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13913,14 +13913,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13937,7 +13937,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13954,7 +13954,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13971,7 +13971,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13988,7 +13988,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -14005,7 +14005,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -14015,14 +14015,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -14039,7 +14039,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14056,7 +14056,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -14073,7 +14073,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -14090,7 +14090,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14107,7 +14107,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14124,7 +14124,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14141,7 +14141,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14151,14 +14151,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14175,7 +14175,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14192,7 +14192,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14202,14 +14202,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14219,14 +14219,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14243,7 +14243,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14260,7 +14260,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14277,7 +14277,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14287,14 +14287,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14311,7 +14311,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14321,14 +14321,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14338,14 +14338,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14362,7 +14362,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14379,7 +14379,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14389,14 +14389,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14413,7 +14413,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14430,7 +14430,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14447,7 +14447,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14464,7 +14464,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14481,7 +14481,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14498,7 +14498,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14515,7 +14515,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14532,7 +14532,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14549,7 +14549,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14559,14 +14559,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14583,7 +14583,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14600,7 +14600,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14617,7 +14617,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14634,7 +14634,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14651,7 +14651,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14668,12 +14668,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -14685,12 +14685,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -14702,12 +14702,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -14719,29 +14719,29 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -14753,12 +14753,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -14770,29 +14770,29 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -14804,12 +14804,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -14821,12 +14821,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -14838,12 +14838,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -14855,7 +14855,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14865,14 +14865,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14882,14 +14882,14 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14906,7 +14906,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14916,14 +14916,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14933,14 +14933,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14957,7 +14957,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14967,14 +14967,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -15008,7 +15008,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -15025,46 +15025,46 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -15076,97 +15076,97 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -15178,24 +15178,24 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -15205,14 +15205,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -15222,14 +15222,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15246,7 +15246,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15256,14 +15256,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15273,14 +15273,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15290,14 +15290,14 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15331,7 +15331,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15348,7 +15348,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15358,14 +15358,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15382,7 +15382,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15392,14 +15392,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15409,14 +15409,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15433,7 +15433,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15443,14 +15443,14 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15460,14 +15460,14 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15477,121 +15477,121 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -15603,58 +15603,58 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15671,7 +15671,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15681,14 +15681,14 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15698,14 +15698,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15722,7 +15722,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15739,7 +15739,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15749,14 +15749,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15773,7 +15773,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15783,14 +15783,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15800,14 +15800,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15817,14 +15817,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15841,7 +15841,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15858,7 +15858,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15875,7 +15875,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15885,14 +15885,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15902,19 +15902,19 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -15926,46 +15926,46 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -15977,12 +15977,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -15994,12 +15994,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -16011,12 +16011,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -16028,58 +16028,58 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -16089,14 +16089,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -16113,7 +16113,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -16130,7 +16130,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -16140,14 +16140,14 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -16157,14 +16157,14 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -16181,7 +16181,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -16191,14 +16191,14 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -16208,14 +16208,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -16232,7 +16232,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16249,7 +16249,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16266,7 +16266,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16276,14 +16276,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16293,14 +16293,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16334,7 +16334,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16351,7 +16351,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16368,7 +16368,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16378,14 +16378,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16395,14 +16395,14 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16412,14 +16412,14 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16429,14 +16429,14 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16446,14 +16446,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16463,14 +16463,14 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16487,7 +16487,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16497,14 +16497,14 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16514,14 +16514,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16531,14 +16531,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16555,7 +16555,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16565,14 +16565,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16589,7 +16589,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16599,14 +16599,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16616,14 +16616,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16640,7 +16640,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16657,7 +16657,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16667,19 +16667,19 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -16691,29 +16691,29 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -16725,46 +16725,46 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -16776,29 +16776,29 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -16810,12 +16810,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -16827,24 +16827,24 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16854,19 +16854,19 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -16878,29 +16878,29 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -16912,46 +16912,46 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -16963,12 +16963,12 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -16980,29 +16980,29 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -17014,46 +17014,46 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -17065,12 +17065,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -17082,46 +17082,46 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -17133,75 +17133,75 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -17218,7 +17218,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -17228,14 +17228,14 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -17252,7 +17252,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -17269,7 +17269,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -17286,7 +17286,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17296,14 +17296,14 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -17313,14 +17313,14 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17330,14 +17330,14 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17354,7 +17354,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17371,7 +17371,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17381,14 +17381,14 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17405,7 +17405,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17415,14 +17415,14 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17439,7 +17439,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17449,14 +17449,14 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17473,7 +17473,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17483,104 +17483,104 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -17592,46 +17592,46 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -17643,12 +17643,12 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -17660,7 +17660,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17670,14 +17670,14 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -17687,14 +17687,14 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17704,14 +17704,14 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -17728,7 +17728,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17745,7 +17745,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -17755,14 +17755,14 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17779,7 +17779,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17789,14 +17789,14 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17806,14 +17806,14 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17823,14 +17823,14 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17847,7 +17847,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17857,14 +17857,14 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17874,14 +17874,14 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17898,7 +17898,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17908,14 +17908,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17925,14 +17925,14 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -17942,14 +17942,14 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17966,7 +17966,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17976,14 +17976,14 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -17993,14 +17993,14 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -18010,7 +18010,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -18044,14 +18044,14 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -18068,7 +18068,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -18078,14 +18078,14 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -18102,12 +18102,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -18119,46 +18119,46 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -18170,46 +18170,46 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -18221,46 +18221,46 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -18272,7 +18272,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -18282,14 +18282,14 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -18306,7 +18306,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -18323,7 +18323,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -18333,14 +18333,14 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18357,7 +18357,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18367,14 +18367,14 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -18391,7 +18391,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -18401,14 +18401,14 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18425,7 +18425,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -18442,7 +18442,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18459,7 +18459,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18476,7 +18476,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18493,7 +18493,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18510,7 +18510,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18520,14 +18520,14 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18544,7 +18544,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18561,7 +18561,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18578,7 +18578,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -18595,7 +18595,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -18612,7 +18612,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -18629,7 +18629,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -18646,7 +18646,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -18663,7 +18663,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -18680,7 +18680,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -18690,14 +18690,14 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -18707,14 +18707,14 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -18724,14 +18724,14 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -18741,14 +18741,14 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -18758,14 +18758,14 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -18782,7 +18782,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -18799,7 +18799,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -18809,14 +18809,14 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -18833,7 +18833,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -18850,7 +18850,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -18867,7 +18867,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -18877,14 +18877,14 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -18901,7 +18901,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -18918,7 +18918,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -18935,7 +18935,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -18952,7 +18952,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -18962,53 +18962,53 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -19020,12 +19020,12 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -19037,12 +19037,12 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -19054,46 +19054,46 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -19105,41 +19105,41 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -19166,14 +19166,14 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -19190,7 +19190,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -19207,7 +19207,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -19217,14 +19217,14 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -19258,7 +19258,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -19268,14 +19268,14 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -19292,7 +19292,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -19309,7 +19309,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -19326,7 +19326,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -19336,14 +19336,14 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -19353,19 +19353,19 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -19377,12 +19377,12 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -19394,12 +19394,12 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -19411,46 +19411,46 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -19462,29 +19462,29 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -19496,12 +19496,12 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -19513,97 +19513,97 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -19615,80 +19615,80 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -19700,17 +19700,187 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>ELES S.p.A.</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>IDNTT S.A.</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>IREN S.p.A.</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>DOTSTAY S.p.A.</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Lemon Sistemi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Met.Extra Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
           <t>Stellantis N.V.</t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>EXPERT.AI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -19738,282 +19908,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BEEWIZE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cloudia Research S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DOTSTAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Datrix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Dexelance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EXPERT.AI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FRENDY ENERGY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IDNTT S.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IREN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Lemon Sistemi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Met.Extra Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>